--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487966_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487966_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9717</v>
+        <v>3.278</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5729</v>
+        <v>4.8028</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3989</v>
+        <v>-1.5248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9139</v>
+        <v>3.2244</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8991</v>
+        <v>-0.3553</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9853</v>
+        <v>3.5797</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2886</v>
+        <v>5.5355</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8834</v>
+        <v>1.9843</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5949</v>
+        <v>3.5512</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3747</v>
+        <v>-2.3112</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0157</v>
+        <v>-2.3397</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3904</v>
+        <v>0.0285</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2561</v>
+        <v>-0.6204</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.0424</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6036</v>
+        <v>0.674</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2487</v>
+        <v>2.2728</v>
       </c>
       <c r="E3" t="n">
-        <v>3.942</v>
+        <v>1.1613</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6933</v>
+        <v>1.1116</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2244</v>
+        <v>-0.2197</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3553</v>
+        <v>-0.7938</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5797</v>
+        <v>0.5742</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5355</v>
+        <v>0.8922</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9843</v>
+        <v>0.471</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5512</v>
+        <v>0.4212</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3112</v>
+        <v>-1.1119</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3397</v>
+        <v>-1.2648</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0285</v>
+        <v>0.1529</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6496</v>
+        <v>0.5103</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8184</v>
+        <v>0.2691</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8312</v>
+        <v>0.2412</v>
       </c>
       <c r="V3" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7521</v>
+        <v>2.0588</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8001</v>
+        <v>1.1654</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.048</v>
+        <v>0.8934</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0601</v>
+        <v>0.9139</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4173</v>
+        <v>1.8991</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6428</v>
+        <v>-0.9853</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0085</v>
+        <v>1.2886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1891</v>
+        <v>1.8834</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1975</v>
+        <v>-0.5949</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0517</v>
+        <v>-0.3747</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6064</v>
+        <v>0.0157</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5547</v>
+        <v>-0.3904</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4247</v>
+        <v>0.3432</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3349</v>
+        <v>0.2644</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0898</v>
+        <v>0.0788</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2946</v>
+        <v>0.169</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3234</v>
+        <v>1.3574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9712</v>
+        <v>-1.1884</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2197</v>
+        <v>-2.0601</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7938</v>
+        <v>-1.4173</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5742</v>
+        <v>-0.6428</v>
       </c>
       <c r="J6" t="n">
+        <v>-1.0085</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.1975</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.0517</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.6064</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5547</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.3876</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3876</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="T6" t="n">
         <v>0.8922</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4212</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-1.1119</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-1.2648</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.1529</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.9822</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9822</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.468</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.5688</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.1008</v>
+        <v>-0.0506</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3282</v>
+        <v>-0.1078</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8663</v>
+        <v>-0.2542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5381</v>
+        <v>0.1464</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2128</v>
+        <v>-0.6349</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4036</v>
+        <v>-0.2274</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8093</v>
+        <v>-0.4075</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6791</v>
+        <v>-0.6388</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6791</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5337</v>
+        <v>0.0039</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4036</v>
+        <v>-0.2677</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1301</v>
+        <v>0.2717</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1512</v>
+        <v>0.5249</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1872</v>
+        <v>0.3846</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3384</v>
+        <v>0.1404</v>
       </c>
       <c r="V7" t="n">
-        <v>0.337</v>
+        <v>-0.1962</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.337</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7014</v>
+        <v>-0.2166</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-1.6693</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0621</v>
+        <v>1.4527</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6349</v>
+        <v>-1.7211</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2274</v>
+        <v>-2.4557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4075</v>
+        <v>0.7346</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6388</v>
+        <v>-1.9461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0404</v>
+        <v>-2.6693</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6791</v>
+        <v>0.7232</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0039</v>
+        <v>0.225</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2677</v>
+        <v>0.2136</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2717</v>
+        <v>0.0114</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.0486</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1248</v>
+        <v>0.0102</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0562</v>
+        <v>0.0384</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1962</v>
+        <v>0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8445</v>
+        <v>-0.4904</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2411</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3966</v>
+        <v>0.3135</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7211</v>
+        <v>-1.2128</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4557</v>
+        <v>-0.4036</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7346</v>
+        <v>-0.8093</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9461</v>
+        <v>-0.6791</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6693</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7232</v>
+        <v>-0.6791</v>
       </c>
       <c r="M9" t="n">
-        <v>0.225</v>
+        <v>-0.5337</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2136</v>
+        <v>-0.4036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0114</v>
+        <v>-0.1301</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5793</v>
+        <v>-0.011</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5616</v>
+        <v>-0.1248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0177</v>
+        <v>0.1138</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2666</v>
+        <v>0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.337</v>
+        <v>-1.5559</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1862</v>
+        <v>-1.4253</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8492</v>
+        <v>-0.1305</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.803</v>
+        <v>-1.6242</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2761</v>
+        <v>-1.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0791</v>
+        <v>-0.5223</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0265</v>
+        <v>-0.6482</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5321</v>
+        <v>0.0271</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5586</v>
+        <v>-0.6752</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7765</v>
+        <v>-0.9761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.256</v>
+        <v>-1.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5205</v>
+        <v>0.1529</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7852</v>
+        <v>-0.5947</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5471</v>
+        <v>-0.3192</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2381</v>
+        <v>-0.2754</v>
       </c>
       <c r="V10" t="n">
         <v>0.2666</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8554</v>
+        <v>-1.6083</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6125</v>
+        <v>-2.4294</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2429</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6242</v>
+        <v>-0.803</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1019</v>
+        <v>0.2761</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5223</v>
+        <v>-1.0791</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6482</v>
+        <v>-0.0265</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0271</v>
+        <v>0.5321</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6752</v>
+        <v>-0.5586</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9761</v>
+        <v>-0.7765</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.129</v>
+        <v>-0.256</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1529</v>
+        <v>-0.5205</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3964</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8942</v>
+        <v>0.5139</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5064</v>
+        <v>0.3039</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3878</v>
+        <v>0.21</v>
       </c>
       <c r="V11" t="n">
         <v>0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1027</v>
+        <v>-1.718</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6672</v>
+        <v>-1.3387</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4354</v>
+        <v>-0.3793</v>
       </c>
       <c r="G12" t="n">
         <v>-2.146</v>
@@ -1390,13 +1390,13 @@
         <v>2.1805</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4125</v>
+        <v>-1.0278</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5064</v>
+        <v>-0.1779</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9061</v>
+        <v>-0.8499</v>
       </c>
       <c r="V12" t="n">
         <v>0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1721</v>
+        <v>-2.9079</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6015</v>
+        <v>-2.6181</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5706</v>
+        <v>-0.2898</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2956</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7377</v>
+        <v>-0.4735</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2351</v>
+        <v>0.2186</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9728</v>
+        <v>-0.6921</v>
       </c>
       <c r="V13" t="n">
         <v>0.2666</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03650000000000109</v>
+        <v>1.284400000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1893</v>
+        <v>0.05869999999999909</v>
       </c>
       <c r="F14" t="n">
         <v>1.2259</v>
@@ -1522,19 +1522,19 @@
         <v>2.331399999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1569999999999996</v>
+        <v>-0.1570000000000005</v>
       </c>
       <c r="L14" t="n">
         <v>2.4886</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.8003</v>
+        <v>-9.800299999999998</v>
       </c>
       <c r="N14" t="n">
         <v>-9.971200000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.171</v>
+        <v>0.1709999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>5.9465</v>
@@ -1546,13 +1546,13 @@
         <v>14.8667</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1927</v>
+        <v>0.0551000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5154</v>
+        <v>1.7635</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7081</v>
+        <v>-1.7082</v>
       </c>
       <c r="V14" t="n">
         <v>2.7514</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5868</v>
+        <v>5.8049</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9822</v>
+        <v>3.5934</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6046</v>
+        <v>2.2115</v>
       </c>
       <c r="G15" t="n">
         <v>3.3564</v>
@@ -1624,13 +1624,13 @@
         <v>1.5858</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2255</v>
+        <v>-0.0074</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8001</v>
+        <v>-0.1889</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5746</v>
+        <v>0.1815</v>
       </c>
       <c r="V15" t="n">
         <v>0.8701</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1065</v>
+        <v>3.0492</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9527</v>
+        <v>2.0358</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1538</v>
+        <v>1.0134</v>
       </c>
       <c r="G16" t="n">
         <v>3.6877</v>
@@ -1702,13 +1702,13 @@
         <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0223</v>
+        <v>-0.0349</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2373</v>
+        <v>0.3204</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2149</v>
+        <v>-0.3553</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3824</v>
+        <v>2.8835</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4366</v>
+        <v>1.8253</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9459</v>
+        <v>1.0582</v>
       </c>
       <c r="G17" t="n">
         <v>1.0325</v>
@@ -1780,13 +1780,13 @@
         <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>1.892</v>
+        <v>1.3931</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3107</v>
+        <v>0.6995</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5813</v>
+        <v>0.6936</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5331</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7827</v>
+        <v>2.7661</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6452</v>
+        <v>2.4601</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1375</v>
+        <v>0.306</v>
       </c>
       <c r="G18" t="n">
         <v>1.931</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1483</v>
+        <v>0.8351</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4661</v>
+        <v>0.3489</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3178</v>
+        <v>0.4863</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1756</v>
+        <v>0.7015</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2008</v>
+        <v>0.8952</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0252</v>
+        <v>-0.1937</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2333</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0036</v>
+        <v>0.5295</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5654</v>
+        <v>0.2598</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4382</v>
+        <v>0.2698</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4562</v>
       </c>
       <c r="E20" t="n">
-        <v>0.487</v>
+        <v>0.6908</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.403</v>
+        <v>-0.2345</v>
       </c>
       <c r="G20" t="n">
         <v>1.0112</v>
@@ -2014,13 +2014,13 @@
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5308</v>
+        <v>0.903</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0883</v>
+        <v>0.292</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4426</v>
+        <v>0.611</v>
       </c>
       <c r="V20" t="n">
         <v>-0.0704</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3057</v>
+        <v>0.1684</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5921</v>
+        <v>-0.2865</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2864</v>
+        <v>0.4549</v>
       </c>
       <c r="G21" t="n">
         <v>1.4555</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6314</v>
+        <v>-1.1573</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6864</v>
+        <v>-0.3808</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.945</v>
+        <v>-0.7765</v>
       </c>
       <c r="V21" t="n">
         <v>0.2666</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2818</v>
+        <v>-2.475</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4673</v>
+        <v>-1.7729</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8144</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9542</v>
@@ -2170,13 +2170,13 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4574</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3782</v>
+        <v>0.0726</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8356</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4538</v>
+        <v>-3.1097</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1726</v>
+        <v>-1.9689</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2812</v>
+        <v>-1.1408</v>
       </c>
       <c r="G23" t="n">
         <v>0.7748</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1781</v>
+        <v>0.1661</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2644</v>
+        <v>0.4682</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4425</v>
+        <v>-0.3021</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4737</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2759</v>
+        <v>-4.1283</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1242</v>
+        <v>-3.9204</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1517</v>
+        <v>-0.2079</v>
       </c>
       <c r="G24" t="n">
         <v>0.0477</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2709</v>
+        <v>-1.1233</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4992</v>
+        <v>-0.2954</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.8279</v>
       </c>
       <c r="V24" t="n">
         <v>-0.674</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8373</v>
+        <v>-6.1533</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5741</v>
+        <v>-4.7778</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2632</v>
+        <v>-1.3755</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6406</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6556</v>
+        <v>0.3396</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3158</v>
+        <v>0.112</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3398</v>
+        <v>0.2275</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4737</v>
@@ -2440,7 +2440,7 @@
         <v>-0.03650000000000109</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2258</v>
+        <v>-1.225899999999999</v>
       </c>
       <c r="F26" t="n">
         <v>1.1895</v>
@@ -2482,13 +2482,13 @@
         <v>8.920099999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>1.1927</v>
+        <v>1.192800000000001</v>
       </c>
       <c r="T26" t="n">
         <v>1.7083</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5154000000000001</v>
+        <v>-0.5153999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.7513</v>
